--- a/out/Attention-Mamba1_repeat_2_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9110100759941124</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.50780289896909</v>
+        <v>11.27907012395075</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.50780289896909</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.50780289896909</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.90780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.90780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.90780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444359</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.486764736444359</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.90780289896909</v>
+        <v>1.286764736444359</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.90780289896909</v>
+        <v>2.159636273578805</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>3.50780289896909</v>
+        <v>2.159636273578805</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.4138931993099121</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.90780289896909</v>
+        <v>0.4138931993099121</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444359</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3110100759941125</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3110100759941125</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.2589783378245343</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245343</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006175633519887924</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.72</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.00321381539106369</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.7899999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.00546659529209137</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.007612228393554688</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.005414612591266632</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.006593286991119385</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.007765021175146103</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00318174809217453</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002347942441701889</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003641679883003235</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.613893199309912</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.006842605769634247</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.008023455739021301</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.005917537957429886</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.007085520774126053</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.007763966917991638</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.007283423095941544</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.006849713623523712</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.007225736975669861</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.008022785186767578</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.007706362754106522</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.007171228528022766</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.008219167590141296</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008373726159334183</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.613893199309912</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0001850277185440063</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.613893199309912</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.003606390208005905</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.613893199309912</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.005359720438718796</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2589783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.004712413996458054</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2589783378245343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.00551249086856842</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.006892971694469452</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.007383193820714951</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.006964020431041718</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.007784102112054825</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.007653605192899704</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.00706113874912262</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005241334438323975</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.001607351005077362</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003177259117364883</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004509314894676208</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0003340616822242737</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.613893199309912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001391053199768066</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.486764736444358</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003964342176914215</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.359636273578805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006056692451238632</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.359636273578805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.004248335957527161</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.359636273578805</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006927330046892166</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.359636273578805</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0005073212087154388</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.359636273578805</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.002230767160654068</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.486764736444359</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0005675777792930603</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.486764736444359</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.001953363418579102</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.286764736444359</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>5.459040403366089e-05</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.159636273578805</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.006525184959173203</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.159636273578805</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.003320302814245224</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.359636273578805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.002522759139537811</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.486764736444358</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0003149211406707764</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.413893199309912</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00163133442401886</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0001485757529735565</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002146691083908081</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001941904425621033</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4138931993099121</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00033583864569664</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4138931993099121</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.000295538455247879</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.16</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0009017772972583771</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.413893199309912</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001373961567878723</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.613893199309912</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0004810169339179993</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001942425966262817</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2589783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-2.111122012138367e-05</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.002025164663791656</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.486764736444358</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.00379311665892601</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.359636273578805</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.001548353582620621</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.486764736444359</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0006779134273529053</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.613893199309912</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.001497760415077209</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00178992748260498</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00152568519115448</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002786010503768921</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002359438687562943</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002919603139162064</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004350468516349792</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004228495061397552</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003577977418899536</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004174243658781052</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.004619628190994263</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004425548017024994</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004247639328241348</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003434032201766968</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.004159577190876007</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003978196531534195</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.004081014543771744</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004868246614933014</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003760870546102524</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003072381019592285</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001010123640298843</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003538839519023895</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003818303346633911</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00271105021238327</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.004050381481647491</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004833050072193146</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005081094801425934</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003265611827373505</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.004462044686079025</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.004719126969575882</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005089584738016129</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004155490547418594</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005516182631254196</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005178190767765045</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.004496555775403976</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005196936428546906</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00502999871969223</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.005153018981218338</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005770929157733917</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005992189049720764</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.005663353949785233</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.006046798080205917</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.005063422024250031</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005761712789535522</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.00552232563495636</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005653716623783112</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005325417965650558</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001850705593824387</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002687692642211914</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.613893199309912</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0004163607954978943</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.613893199309912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002305313944816589</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.613893199309912</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001107320189476013</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.2589783378245343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002908796072006226</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2589783378245343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003420542925596237</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4589783378245343</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002681098878383636</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003813263028860092</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00184013694524765</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4589783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_2_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.006175633519887924</v>
+        <v>-0.006175670772790909</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.72</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.00321381539106369</v>
+        <v>-0.003213807940483093</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7899999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.00546659529209137</v>
+        <v>-0.005466591566801071</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.007612228393554688</v>
+        <v>-0.007612209767103195</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.005414612591266632</v>
+        <v>-0.005414631217718124</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.006593286991119385</v>
+        <v>-0.006593313068151474</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.007765021175146103</v>
+        <v>-0.007765024900436401</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.00318174809217453</v>
+        <v>-0.003181759268045425</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.002347942441701889</v>
+        <v>0.002347931265830994</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.003641679883003235</v>
+        <v>-0.003641653805971146</v>
       </c>
       <c r="JB11" t="n">
         <v>0.02000000000000007</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.006842605769634247</v>
+        <v>-0.006842624396085739</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.1199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.008023455739021301</v>
+        <v>-0.008023466914892197</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.005917537957429886</v>
+        <v>-0.005917534232139587</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.007085520774126053</v>
+        <v>-0.007085535675287247</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.007763966917991638</v>
+        <v>-0.007764007896184921</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.007283423095941544</v>
+        <v>-0.007283404469490051</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.006849713623523712</v>
+        <v>-0.006849721074104309</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.007225736975669861</v>
+        <v>-0.007225710898637772</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.008022785186767578</v>
+        <v>-0.008022777736186981</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.007706362754106522</v>
+        <v>-0.007706340402364731</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.007171228528022766</v>
+        <v>-0.007171224802732468</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.008219167590141296</v>
+        <v>-0.008219148963689804</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.008373726159334183</v>
+        <v>-0.00837370753288269</v>
       </c>
       <c r="JB24" t="n">
         <v>0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0001850277185440063</v>
+        <v>0.0001849830150604248</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.003606390208005905</v>
+        <v>-0.003606408834457397</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.005359720438718796</v>
+        <v>-0.005359787493944168</v>
       </c>
       <c r="JB27" t="n">
         <v>0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.004712413996458054</v>
+        <v>-0.004712380468845367</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.00551249086856842</v>
+        <v>-0.005512505769729614</v>
       </c>
       <c r="JB29" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.006892971694469452</v>
+        <v>-0.006892979145050049</v>
       </c>
       <c r="JB30" t="n">
         <v>0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.007383193820714951</v>
+        <v>-0.007383197546005249</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.007784102112054825</v>
+        <v>-0.007784105837345123</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.007653605192899704</v>
+        <v>-0.007653601467609406</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.005241334438323975</v>
+        <v>-0.005241349339485168</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.004509314894676208</v>
+        <v>-0.004509307444095612</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0003340616822242737</v>
+        <v>-0.0003340765833854675</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.003964342176914215</v>
+        <v>0.00396433100104332</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.006056692451238632</v>
+        <v>0.006056699901819229</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.004248335957527161</v>
+        <v>0.004248328506946564</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.006927330046892166</v>
+        <v>0.006927337497472763</v>
       </c>
       <c r="JB45" t="n">
         <v>0.1199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0005073212087154388</v>
+        <v>0.0005073584616184235</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.02000000000000007</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.002230767160654068</v>
+        <v>0.002230759710073471</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.16</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0005675777792930603</v>
+        <v>-0.0005675517022609711</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.001953363418579102</v>
+        <v>0.001953344792127609</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>5.459040403366089e-05</v>
+        <v>5.459412932395935e-05</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.006525184959173203</v>
+        <v>0.006525147706270218</v>
       </c>
       <c r="JB51" t="n">
         <v>0.1199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.003320302814245224</v>
+        <v>0.003320273011922836</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.002522759139537811</v>
+        <v>0.002522747963666916</v>
       </c>
       <c r="JB53" t="n">
         <v>0.5799999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0003149211406707764</v>
+        <v>-0.0003149323165416718</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.00163133442401886</v>
+        <v>-0.001631315797567368</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0001485757529735565</v>
+        <v>-0.0001485869288444519</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002146691083908081</v>
+        <v>-0.002146676182746887</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.5799999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.001941904425621033</v>
+        <v>-0.001941930502653122</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.00033583864569664</v>
+        <v>0.0003358349204063416</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.000295538455247879</v>
+        <v>-0.0002955682575702667</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0009017772972583771</v>
+        <v>-0.0009017996490001678</v>
       </c>
       <c r="JB61" t="n">
         <v>0.4399999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.001373961567878723</v>
+        <v>0.001373987644910812</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1600000000000001</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001942425966262817</v>
+        <v>-0.001942433416843414</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-2.111122012138367e-05</v>
+        <v>-2.114102244377136e-05</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.002025164663791656</v>
+        <v>0.002025175839662552</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.00379311665892601</v>
+        <v>0.003793109208345413</v>
       </c>
       <c r="JB67" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.001548353582620621</v>
+        <v>0.001548342406749725</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0006779134273529053</v>
+        <v>-0.0006779208779335022</v>
       </c>
       <c r="JB69" t="n">
         <v>0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.001497760415077209</v>
+        <v>-0.001497782766819</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00178992748260498</v>
+        <v>-0.001789916306734085</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00152568519115448</v>
+        <v>-0.001525666564702988</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002786010503768921</v>
+        <v>-0.002785976976156235</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002359438687562943</v>
+        <v>-0.002359434962272644</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002919603139162064</v>
+        <v>-0.002919618040323257</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004350468516349792</v>
+        <v>-0.004350461065769196</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004228495061397552</v>
+        <v>-0.004228487610816956</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003577977418899536</v>
+        <v>-0.00357799232006073</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.004174243658781052</v>
+        <v>-0.004174232482910156</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.004425548017024994</v>
+        <v>-0.004425536841154099</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.004247639328241348</v>
+        <v>-0.004247646778821945</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003434032201766968</v>
+        <v>-0.003434013575315475</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.004159577190876007</v>
+        <v>-0.004159566015005112</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003978196531534195</v>
+        <v>-0.003978170454502106</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.004081014543771744</v>
+        <v>-0.004081010818481445</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.004868246614933014</v>
+        <v>-0.004868261516094208</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003760870546102524</v>
+        <v>-0.003760859370231628</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001010123640298843</v>
+        <v>-0.00101010873913765</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.003538839519023895</v>
+        <v>-0.003538817167282104</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003818303346633911</v>
+        <v>-0.003818299621343613</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.00271105021238327</v>
+        <v>-0.002711031585931778</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3999999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.004833050072193146</v>
+        <v>-0.004833042621612549</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.8599999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.005081094801425934</v>
+        <v>-0.005081102252006531</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.003265611827373505</v>
+        <v>-0.003265630453824997</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.004462044686079025</v>
+        <v>-0.004462029784917831</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.8599999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.004719126969575882</v>
+        <v>-0.004719119518995285</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005089584738016129</v>
+        <v>-0.005089607089757919</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.004155490547418594</v>
+        <v>-0.004155497997999191</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005516182631254196</v>
+        <v>-0.005516201257705688</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.005178190767765045</v>
+        <v>-0.005178187042474747</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.004496555775403976</v>
+        <v>-0.004496574401855469</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.005196936428546906</v>
+        <v>-0.005196914076805115</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.00502999871969223</v>
+        <v>-0.005030006170272827</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.005153018981218338</v>
+        <v>-0.005152996629476547</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.005770929157733917</v>
+        <v>-0.005770951509475708</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.005992189049720764</v>
+        <v>-0.005992166697978973</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.005663353949785233</v>
+        <v>-0.005663342773914337</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.006046798080205917</v>
+        <v>-0.006046783179044724</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.005063422024250031</v>
+        <v>-0.005063407123088837</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.005761712789535522</v>
+        <v>-0.005761697888374329</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.00552232563495636</v>
+        <v>-0.005522340536117554</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.005653716623783112</v>
+        <v>-0.005653694272041321</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.1199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.005325417965650558</v>
+        <v>-0.005325447767972946</v>
       </c>
       <c r="JB116" t="n">
         <v>0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.001850705593824387</v>
+        <v>-0.001850694417953491</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002687692642211914</v>
+        <v>-0.002687722444534302</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0004163607954978943</v>
+        <v>0.0004163570702075958</v>
       </c>
       <c r="JB119" t="n">
         <v>0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002305313944816589</v>
+        <v>-0.002305310219526291</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.001107320189476013</v>
+        <v>-0.001107323914766312</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002908796072006226</v>
+        <v>-0.002908792346715927</v>
       </c>
       <c r="JB122" t="n">
         <v>0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003420542925596237</v>
+        <v>-0.003420561552047729</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002681098878383636</v>
+        <v>-0.002681069076061249</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003813263028860092</v>
+        <v>-0.003813296556472778</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.00184013694524765</v>
+        <v>-0.001840103417634964</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>
